--- a/outputs/other/silpo_novus/primary_chain_output.xlsx
+++ b/outputs/other/silpo_novus/primary_chain_output.xlsx
@@ -23,7 +23,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -62,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +503,11 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>cointegration_p</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pair_n_obs</t>
         </is>
       </c>
     </row>
@@ -538,6 +547,7 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -545,19 +555,31 @@
           <t>prozorro</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0.9029715543675231</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.373451018408759e-14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.260173359802745e-10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ambiguous</t>
+          <t>I(1)</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -575,6 +597,7 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -582,15 +605,27 @@
           <t>retail</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>0.1377484622022294</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.02230468906736149</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.056387455335942e-08</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ambiguous</t>
+          <t>I(1)</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -612,6 +647,7 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -647,6 +683,9 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -681,7 +720,12 @@
           <t>promo_controlled</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>1.162757574361686e-06</v>
+      </c>
+      <c r="N6" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -717,6 +761,9 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -729,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,34 +899,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>prozorro_to_retail</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ARDL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>prozorro</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.191807377212619</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-12.70081452552591</v>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -887,18 +938,100 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>bounds_lower_p=0.001596; bounds_upper_p=0.006679; max_lag_try=14</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NARDL</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>retail</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>prozorro</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7522139284224689</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.209165049284258</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.4291476640555171</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.00407796931835764</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.859423951247572</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.4819111926141287</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>unreliable</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>No admissible model estimated for this retailer/variant in aligned sample.</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Wald short/long asymmetry reported; dynamic multipliers saved.</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>Primary chain is strictly ProducerUA -&gt; ProZorro -&gt; Retail. Retail is estimated separately for silpo, novus, and silpo_novus. Combined rule: daily median of available silpo and novus standardized_type prices.</t>
         </is>
@@ -915,7 +1048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,28 +1096,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ARDL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>prozorro_to_retail</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>prozorro</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.389263947975623</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1028376278186526</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.894300321098457</v>
+      </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NARDL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>retail</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>prozorro</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2397663534427097</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005946756007259149</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.260837456608593e-56</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -999,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1041,6 +1214,7190 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>combined_rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45761</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>5.295</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45763</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>4.985</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45764</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45765</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>5.175000000000001</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45768</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45769</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45770</v>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45771</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>5.235</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45772</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45775</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45776</v>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>4.775</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45779</v>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45782</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>4.995</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45784</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45785</v>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45786</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>4.675000000000001</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45789</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45790</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>4.890000000000001</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45791</v>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45793</v>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45796</v>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>4.715</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45797</v>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="n">
+        <v>4.545</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45798</v>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45799</v>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45800</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="n">
+        <v>5.265000000000001</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45802</v>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45803</v>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45804</v>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45805</v>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45806</v>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45807</v>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="n">
+        <v>4.700000000000001</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45813</v>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45814</v>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>4.850000000000001</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45815</v>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45817</v>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="n">
+        <v>4.845000000000001</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45818</v>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45819</v>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45820</v>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45821</v>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45822</v>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="n">
+        <v>4.920000000000001</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45824</v>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="n">
+        <v>4.484999999999999</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45825</v>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45826</v>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="n">
+        <v>4.520000000000001</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45827</v>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45828</v>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45829</v>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45831</v>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45832</v>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45833</v>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="n">
+        <v>4.775</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45834</v>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="n">
+        <v>4.800000000000001</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="n">
+        <v>4.529999999999999</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45840</v>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45841</v>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45842</v>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45845</v>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45846</v>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="n">
+        <v>5.315</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45847</v>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="n">
+        <v>5.140000000000001</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45848</v>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45849</v>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45851</v>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45852</v>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="n">
+        <v>5.395000000000001</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45854</v>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="n">
+        <v>5.220000000000001</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="n">
+        <v>5.300000000000001</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45858</v>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45860</v>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="n">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="n">
+        <v>5.170000000000001</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45878</v>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="n">
+        <v>5.385</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="n">
+        <v>4.955</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45886</v>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="n">
+        <v>5.245</v>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45892</v>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45893</v>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="n">
+        <v>5.195</v>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="n">
+        <v>5.245000000000001</v>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="n">
+        <v>5.279999999999999</v>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="n">
+        <v>5.865</v>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="n">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45913</v>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="n">
+        <v>5.190000000000001</v>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="n">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>45920</v>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="n">
+        <v>5.390000000000001</v>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="n">
+        <v>5.595000000000001</v>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45927</v>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="n">
+        <v>4.850000000000001</v>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45928</v>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="n">
+        <v>6</v>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>45942</v>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="n">
+        <v>6</v>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="n">
+        <v>6</v>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="D157" t="n">
+        <v>55.49</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D158" t="n">
+        <v>66.11499999999999</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="D159" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="n">
+        <v>6</v>
+      </c>
+      <c r="D160" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="D161" t="n">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45956</v>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="n">
+        <v>64.23999999999999</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="D163" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="n">
+        <v>6.695</v>
+      </c>
+      <c r="D164" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="D165" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="D166" t="n">
+        <v>62.445</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D167" t="n">
+        <v>65.98999999999999</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="D168" t="n">
+        <v>64.23999999999999</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>45963</v>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="n">
+        <v>6</v>
+      </c>
+      <c r="D169" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D170" t="n">
+        <v>63.49</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D171" t="n">
+        <v>81.80499999999999</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="D172" t="n">
+        <v>82.73999999999999</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="D173" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="n">
+        <v>6.380000000000001</v>
+      </c>
+      <c r="D174" t="n">
+        <v>66.66</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>45969</v>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="n">
+        <v>66.82499999999999</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>45970</v>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="n">
+        <v>6.925</v>
+      </c>
+      <c r="D176" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="D177" t="n">
+        <v>65.98999999999999</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="D178" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D179" t="n">
+        <v>63.62</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="D180" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="D181" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="n">
+        <v>6.470000000000001</v>
+      </c>
+      <c r="D182" t="n">
+        <v>70.48999999999999</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D184" t="n">
+        <v>69.48999999999999</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D185" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="D186" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="D187" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D188" t="n">
+        <v>67.73999999999999</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>45983</v>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="D189" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="n">
+        <v>6.225</v>
+      </c>
+      <c r="D190" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="D191" t="n">
+        <v>66.66</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="D192" t="n">
+        <v>62.645</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="D193" t="n">
+        <v>86.745</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="n">
+        <v>6.970000000000001</v>
+      </c>
+      <c r="D194" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="D195" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="D196" t="n">
+        <v>65.98999999999999</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D197" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="n">
+        <v>6.885</v>
+      </c>
+      <c r="D198" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="D199" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D200" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D201" t="n">
+        <v>60.49</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="D202" t="n">
+        <v>86.47</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>45997</v>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="D203" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>45998</v>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D205" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="D206" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="D207" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="D208" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="n">
+        <v>6.609999999999999</v>
+      </c>
+      <c r="D209" t="n">
+        <v>128.495</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>46004</v>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="n">
+        <v>7.140000000000001</v>
+      </c>
+      <c r="D210" t="n">
+        <v>58.74</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="n">
+        <v>6.835</v>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="n">
+        <v>6.859999999999999</v>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="n">
+        <v>6.300000000000001</v>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46011</v>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="n">
+        <v>6.625</v>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46018</v>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="n">
+        <v>6.390000000000001</v>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46019</v>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46025</v>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="n">
+        <v>5.975</v>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="n">
+        <v>6</v>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="n">
+        <v>6</v>
+      </c>
+      <c r="D234" t="n">
+        <v>92.48999999999999</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="n">
+        <v>6</v>
+      </c>
+      <c r="D236" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="n">
+        <v>7</v>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
         </is>
       </c>
     </row>
@@ -1055,9 +8412,417 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>lag</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0218016234751243</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.1677317854495336</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.1861499791272798</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.1195477382415461</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.3024125191964572</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.3584160123905419</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.256406254168928</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.1584587704221817</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.3378266814360856</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.1559645946222167</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.1587338643399071</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.244078537874973</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.2191276584924703</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.09053412649840303</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.01937714575852243</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.02852223306612441</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.01115658309759503</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.05490922876379749</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.2024535498474835</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.136949728565266</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.09355059469842485</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.02486717376183442</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.03998824770032249</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.02962642392675777</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.02205230193637782</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.08309220249709504</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.1647258314066488</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.1659740139285852</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.1239481306909523</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.174293675953553</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1068,7 +8833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,10 +8874,35 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>n_obs_producer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_obs_prozorro</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>n_obs_retail</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>n_obs_pair_prod_prozorro</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>n_obs_pair_prozorro_retail</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>any_i2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>eligibility_note</t>
         </is>
@@ -1136,7 +8926,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1146,20 +8936,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ambiguous</t>
+          <t>I(1)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ambiguous</t>
+          <t>I(1)</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Insufficient common sample after alignment; model outputs are placeholders.</t>
+      <c r="I2" t="n">
+        <v>232</v>
+      </c>
+      <c r="J2" t="n">
+        <v>56</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>52</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Low pair overlap in main chain links (min pair n_obs=0). Daily estimation kept; long-run identification may be weak.</t>
         </is>
       </c>
     </row>
@@ -1174,9 +8979,368 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>horizon</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>mult_pos</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mult_neg</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1.205618255494476</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.957832183916945</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-1.362521157383362</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-2.21263054124775</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-1.382940988046142</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-2.245790790339472</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-1.385598488189714</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-2.250106368082376</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-1.385944343507014</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-2.25066801076496</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-1.385989354191508</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-2.250741104686954</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-1.385995212021696</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-2.250750617356839</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-1.385995974377899</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-2.250751855365224</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-1.385996073593302</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-2.250752016483478</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-1.385996086505502</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-2.250752037451908</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-1.385996088185936</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-2.250752040180804</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-1.385996088404633</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-2.250752040535951</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-1.385996088433095</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-2.250752040582171</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-1.385996088436799</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-2.250752040588186</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-1.385996088437281</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-2.250752040588969</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-1.385996088437344</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-2.250752040589071</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-1.385996088437352</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-2.250752040589084</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-1.385996088437353</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-2.250752040589086</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-1.385996088437353</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-2.250752040589086</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-1.385996088437353</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-2.250752040589086</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-1.385996088437353</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-2.250752040589086</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>prozorro_to_retail</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/outputs/other/silpo_novus/primary_chain_output.xlsx
+++ b/outputs/other/silpo_novus/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9029715543675231</v>
+        <v>0.9029715543675233</v>
       </c>
       <c r="C3" t="n">
         <v>0.01</v>
       </c>
       <c r="D3" t="n">
-        <v>1.373451018408759e-14</v>
+        <v>1.373451018408814e-14</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.260173359802745e-10</v>
+        <v>1.26017335980257e-10</v>
       </c>
       <c r="G3" t="n">
         <v>0.1</v>
@@ -612,13 +612,13 @@
         <v>0.1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02230468906736149</v>
+        <v>0.02230468906736146</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>1.056387455335942e-08</v>
+        <v>1.056387455335973e-08</v>
       </c>
       <c r="G4" t="n">
         <v>0.1</v>
@@ -926,10 +926,10 @@
         <v>52</v>
       </c>
       <c r="J2" t="n">
-        <v>3.191807377212619</v>
+        <v>3.191807377212628</v>
       </c>
       <c r="K2" t="n">
-        <v>-12.70081452552591</v>
+        <v>-12.70081452552557</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -1000,22 +1000,22 @@
         <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7522139284224689</v>
+        <v>0.7522139284224749</v>
       </c>
       <c r="K3" t="n">
-        <v>6.209165049284258</v>
+        <v>6.209165049284259</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4291476640555171</v>
+        <v>-0.4291476640555165</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00407796931835764</v>
+        <v>0.004077969318357453</v>
       </c>
       <c r="N3" t="n">
-        <v>0.859423951247572</v>
+        <v>0.8594239512475649</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4819111926141287</v>
+        <v>0.4819111926141088</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.389263947975623</v>
+        <v>0.389263947975609</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1028376278186526</v>
+        <v>0.102837627818659</v>
       </c>
       <c r="G2" t="n">
-        <v>0.894300321098457</v>
+        <v>0.8943003210984833</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.2397663534427097</v>
+        <v>0.2397663534427088</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005946756007259149</v>
+        <v>0.005946756007259094</v>
       </c>
       <c r="G3" t="n">
-        <v>6.260837456608593e-56</v>
+        <v>6.260837456607158e-56</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -9009,10 +9009,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.205618255494476</v>
+        <v>-1.205618255494473</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.957832183916945</v>
+        <v>-1.957832183916948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -9025,10 +9025,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.362521157383362</v>
+        <v>-1.362521157383359</v>
       </c>
       <c r="C3" t="n">
-        <v>-2.21263054124775</v>
+        <v>-2.212630541247754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -9041,10 +9041,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.382940988046142</v>
+        <v>-1.382940988046139</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.245790790339472</v>
+        <v>-2.245790790339477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -9057,10 +9057,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.385598488189714</v>
+        <v>-1.385598488189711</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.250106368082376</v>
+        <v>-2.25010636808238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -9073,10 +9073,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.385944343507014</v>
+        <v>-1.385944343507011</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.25066801076496</v>
+        <v>-2.250668010764965</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -9089,10 +9089,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.385989354191508</v>
+        <v>-1.385989354191505</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.250741104686954</v>
+        <v>-2.250741104686959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -9105,10 +9105,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.385995212021696</v>
+        <v>-1.385995212021694</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.250750617356839</v>
+        <v>-2.250750617356843</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.385995974377899</v>
+        <v>-1.385995974377897</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.250751855365224</v>
+        <v>-2.250751855365229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -9137,10 +9137,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.385996073593302</v>
+        <v>-1.385996073593299</v>
       </c>
       <c r="C10" t="n">
-        <v>-2.250752016483478</v>
+        <v>-2.250752016483482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -9153,10 +9153,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.385996086505502</v>
+        <v>-1.3859960865055</v>
       </c>
       <c r="C11" t="n">
-        <v>-2.250752037451908</v>
+        <v>-2.250752037451912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -9169,10 +9169,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.385996088185936</v>
+        <v>-1.385996088185933</v>
       </c>
       <c r="C12" t="n">
-        <v>-2.250752040180804</v>
+        <v>-2.250752040180809</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9185,10 +9185,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.385996088404633</v>
+        <v>-1.38599608840463</v>
       </c>
       <c r="C13" t="n">
-        <v>-2.250752040535951</v>
+        <v>-2.250752040535956</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9201,10 +9201,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.385996088433095</v>
+        <v>-1.385996088433092</v>
       </c>
       <c r="C14" t="n">
-        <v>-2.250752040582171</v>
+        <v>-2.250752040582176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -9217,10 +9217,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.385996088436799</v>
+        <v>-1.385996088436796</v>
       </c>
       <c r="C15" t="n">
-        <v>-2.250752040588186</v>
+        <v>-2.250752040588191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -9233,10 +9233,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.385996088437281</v>
+        <v>-1.385996088437278</v>
       </c>
       <c r="C16" t="n">
-        <v>-2.250752040588969</v>
+        <v>-2.250752040588974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -9249,10 +9249,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.385996088437344</v>
+        <v>-1.385996088437341</v>
       </c>
       <c r="C17" t="n">
-        <v>-2.250752040589071</v>
+        <v>-2.250752040589076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9265,10 +9265,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.385996088437352</v>
+        <v>-1.385996088437349</v>
       </c>
       <c r="C18" t="n">
-        <v>-2.250752040589084</v>
+        <v>-2.250752040589089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9281,10 +9281,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.385996088437353</v>
+        <v>-1.38599608843735</v>
       </c>
       <c r="C19" t="n">
-        <v>-2.250752040589086</v>
+        <v>-2.250752040589091</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9297,10 +9297,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.385996088437353</v>
+        <v>-1.385996088437351</v>
       </c>
       <c r="C20" t="n">
-        <v>-2.250752040589086</v>
+        <v>-2.250752040589091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9313,10 +9313,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.385996088437353</v>
+        <v>-1.385996088437351</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.250752040589086</v>
+        <v>-2.250752040589091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -9329,10 +9329,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.385996088437353</v>
+        <v>-1.385996088437351</v>
       </c>
       <c r="C22" t="n">
-        <v>-2.250752040589086</v>
+        <v>-2.250752040589091</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
